--- a/output/models and plots/abund_model_table.xlsx
+++ b/output/models and plots/abund_model_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6C1E72-3EAE-5048-AC3E-59331BCD13D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891BE748-21E7-D74D-8E26-0BA8B329720E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2680" yWindow="4020" windowWidth="24940" windowHeight="12440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/output/models and plots/abund_model_table.xlsx
+++ b/output/models and plots/abund_model_table.xlsx
@@ -1,62 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891BE748-21E7-D74D-8E26-0BA8B329720E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="4020" windowWidth="24940" windowHeight="12440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>formula</t>
-  </si>
-  <si>
-    <t>No_Par</t>
-  </si>
-  <si>
-    <t>logLik</t>
-  </si>
-  <si>
-    <t>AICc</t>
-  </si>
-  <si>
-    <t>Delta_AICc</t>
-  </si>
-  <si>
-    <t>wi_AICc</t>
-  </si>
-  <si>
-    <t>total_abundance ~ bait + canopy + (1 | location)</t>
-  </si>
-  <si>
-    <t>total_abundance ~ bait + canopy + mean_relief + sd_relief + depth +     (1 | location)</t>
-  </si>
-  <si>
-    <t>total_abundance ~ bait + macroalgae + (1 | location)</t>
-  </si>
-  <si>
-    <t>total_abundance ~ macroalgae + scytothalia + canopy + ecklonia +     mean_relief + sd_relief + depth + bait + (1 | location)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -156,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -190,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -401,114 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="90.5" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K72"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>predictors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AICc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RDF</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n_predictors</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>adjAICc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>deltaAICc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>delta_adjAICc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>canopy</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>953.0810578127591</v>
+      </c>
+      <c r="D2">
+        <v>-470.0889160031538</v>
+      </c>
+      <c r="G2">
+        <v>94</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>955.0810578127591</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ecklonia</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>955.6867552613301</v>
+      </c>
+      <c r="D3">
+        <v>-471.3917647274392</v>
+      </c>
+      <c r="G3">
+        <v>94</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I3">
+        <v>957.6867552613301</v>
+      </c>
+      <c r="J3">
+        <v>2.605697448570936</v>
+      </c>
+      <c r="K3">
+        <v>2.605697448570936</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + depth + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>depth + canopy</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>954.2708360183402</v>
+      </c>
+      <c r="D4">
+        <v>-469.5267223569962</v>
+      </c>
+      <c r="G4">
+        <v>93</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>-470.089</v>
-      </c>
-      <c r="D2">
-        <v>953.08100000000002</v>
-      </c>
-      <c r="E2">
+      <c r="I4">
+        <v>958.2708360183402</v>
+      </c>
+      <c r="J4">
+        <v>1.189778205581092</v>
+      </c>
+      <c r="K4">
+        <v>3.189778205581092</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + scytothalia + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>954.3503585352387</v>
+      </c>
+      <c r="D5">
+        <v>-469.5664836154454</v>
+      </c>
+      <c r="G5">
+        <v>93</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>958.3503585352387</v>
+      </c>
+      <c r="J5">
+        <v>1.269300722479556</v>
+      </c>
+      <c r="K5">
+        <v>3.269300722479556</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + mean_relief + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>954.6026208936614</v>
+      </c>
+      <c r="D6">
+        <v>-469.6926147946568</v>
+      </c>
+      <c r="G6">
+        <v>93</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>958.6026208936614</v>
+      </c>
+      <c r="J6">
+        <v>1.521563080902297</v>
+      </c>
+      <c r="K6">
+        <v>3.521563080902297</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + sd_relief + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sd_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>955.2965264149479</v>
+      </c>
+      <c r="D7">
+        <v>-470.0395675553</v>
+      </c>
+      <c r="G7">
+        <v>93</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>959.2965264149479</v>
+      </c>
+      <c r="J7">
+        <v>2.215468602188821</v>
+      </c>
+      <c r="K7">
+        <v>4.215468602188821</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + depth + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>depth + ecklonia</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>956.7519376344875</v>
+      </c>
+      <c r="D8">
+        <v>-470.7672731650698</v>
+      </c>
+      <c r="G8">
+        <v>93</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>960.7519376344875</v>
+      </c>
+      <c r="J8">
+        <v>3.670879821728363</v>
+      </c>
+      <c r="K8">
+        <v>5.670879821728363</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + mean_relief + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mean_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>956.9644248797443</v>
+      </c>
+      <c r="D9">
+        <v>-470.8735167876982</v>
+      </c>
+      <c r="G9">
+        <v>93</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>960.9644248797443</v>
+      </c>
+      <c r="J9">
+        <v>3.883367066985215</v>
+      </c>
+      <c r="K9">
+        <v>5.883367066985215</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + sd_relief + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sd_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>957.0832224267414</v>
+      </c>
+      <c r="D10">
+        <v>-470.9329155611968</v>
+      </c>
+      <c r="G10">
+        <v>93</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>961.0832224267414</v>
+      </c>
+      <c r="J10">
+        <v>4.002164613982245</v>
+      </c>
+      <c r="K10">
+        <v>6.002164613982245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + scytothalia + ecklonia + (1 | </t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>depth + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>955.2849129681564</v>
+      </c>
+      <c r="D11">
+        <v>-468.8512476928694</v>
+      </c>
+      <c r="G11">
+        <v>92</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>961.2849129681564</v>
+      </c>
+      <c r="J11">
+        <v>2.203855155397264</v>
+      </c>
+      <c r="K11">
+        <v>6.203855155397264</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>depth + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>955.2849129681564</v>
+      </c>
+      <c r="D12">
+        <v>-468.8512476928694</v>
+      </c>
+      <c r="G12">
+        <v>92</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>961.2849129681564</v>
+      </c>
+      <c r="J12">
+        <v>2.203855155397264</v>
+      </c>
+      <c r="K12">
+        <v>6.203855155397264</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + macroalgae + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>957.3911671995044</v>
+      </c>
+      <c r="D13">
+        <v>-471.0868879475782</v>
+      </c>
+      <c r="G13">
+        <v>93</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>961.3911671995044</v>
+      </c>
+      <c r="J13">
+        <v>4.310109386745239</v>
+      </c>
+      <c r="K13">
+        <v>6.310109386745239</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + mean_relief + canopy + (1 | </t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>955.6427779384095</v>
+      </c>
+      <c r="D14">
+        <v>-469.0301801779959</v>
+      </c>
+      <c r="G14">
+        <v>92</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>961.6427779384095</v>
+      </c>
+      <c r="J14">
+        <v>2.561720125650368</v>
+      </c>
+      <c r="K14">
+        <v>6.561720125650368</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>955.6427779384095</v>
+      </c>
+      <c r="D15">
+        <v>-469.0301801779959</v>
+      </c>
+      <c r="G15">
+        <v>92</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
+        <v>961.6427779384095</v>
+      </c>
+      <c r="J15">
+        <v>2.561720125650368</v>
+      </c>
+      <c r="K15">
+        <v>6.561720125650368</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + scytothalia + macroalgae + ecklonia + </t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>scytothalia + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>955.751174120241</v>
+      </c>
+      <c r="D16">
+        <v>-469.0843782689117</v>
+      </c>
+      <c r="G16">
+        <v>92</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>961.751174120241</v>
+      </c>
+      <c r="J16">
+        <v>2.670116307481862</v>
+      </c>
+      <c r="K16">
+        <v>6.670116307481862</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>scytothalia + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>955.751174120241</v>
+      </c>
+      <c r="D17">
+        <v>-469.0843782689117</v>
+      </c>
+      <c r="G17">
+        <v>92</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>961.751174120241</v>
+      </c>
+      <c r="J17">
+        <v>2.670116307481862</v>
+      </c>
+      <c r="K17">
+        <v>6.670116307481862</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>macroalgae</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>960.1120051280024</v>
+      </c>
+      <c r="D18">
+        <v>-473.6043896607754</v>
+      </c>
+      <c r="G18">
+        <v>94</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>962.1120051280024</v>
+      </c>
+      <c r="J18">
+        <v>7.030947315243225</v>
+      </c>
+      <c r="K18">
+        <v>7.030947315243225</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + mean_relief + scytothalia + ecklonia + </t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>956.235871675913</v>
+      </c>
+      <c r="D19">
+        <v>-469.3267270467477</v>
+      </c>
+      <c r="G19">
+        <v>92</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>962.235871675913</v>
+      </c>
+      <c r="J19">
+        <v>3.15481386315389</v>
+      </c>
+      <c r="K19">
+        <v>7.15481386315389</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>956.235871675913</v>
+      </c>
+      <c r="D20">
+        <v>-469.3267270467477</v>
+      </c>
+      <c r="G20">
+        <v>92</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <v>962.235871675913</v>
+      </c>
+      <c r="J20">
+        <v>3.15481386315389</v>
+      </c>
+      <c r="K20">
+        <v>7.15481386315389</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + sd_relief + scytothalia + ecklonia + </t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>956.329881899405</v>
+      </c>
+      <c r="D21">
+        <v>-469.3737321584937</v>
+      </c>
+      <c r="G21">
+        <v>92</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>962.329881899405</v>
+      </c>
+      <c r="J21">
+        <v>3.248824086645868</v>
+      </c>
+      <c r="K21">
+        <v>7.248824086645868</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>956.329881899405</v>
+      </c>
+      <c r="D22">
+        <v>-469.3737321584937</v>
+      </c>
+      <c r="G22">
+        <v>92</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>962.329881899405</v>
+      </c>
+      <c r="J22">
+        <v>3.248824086645868</v>
+      </c>
+      <c r="K22">
+        <v>7.248824086645868</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + depth + sd_relief + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>956.6338197364969</v>
+      </c>
+      <c r="D23">
+        <v>-469.5257010770396</v>
+      </c>
+      <c r="G23">
+        <v>92</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>962.6338197364969</v>
+      </c>
+      <c r="J23">
+        <v>3.552761923737762</v>
+      </c>
+      <c r="K23">
+        <v>7.552761923737762</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + mean_relief + sd_relief + canopy + (1 | </t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>956.684681333973</v>
+      </c>
+      <c r="D24">
+        <v>-469.5511318757777</v>
+      </c>
+      <c r="G24">
+        <v>92</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>962.684681333973</v>
+      </c>
+      <c r="J24">
+        <v>3.603623521213876</v>
+      </c>
+      <c r="K24">
+        <v>7.603623521213876</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>956.684681333973</v>
+      </c>
+      <c r="D25">
+        <v>-469.5511318757777</v>
+      </c>
+      <c r="G25">
+        <v>92</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>962.684681333973</v>
+      </c>
+      <c r="J25">
+        <v>3.603623521213876</v>
+      </c>
+      <c r="K25">
+        <v>7.603623521213876</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>963.2520087882961</v>
+      </c>
+      <c r="D26">
+        <v>-476.3068554579778</v>
+      </c>
+      <c r="G26">
+        <v>95</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>0.88300000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>-468.99299999999999</v>
-      </c>
-      <c r="D3">
-        <v>957.98500000000001</v>
-      </c>
-      <c r="E3">
-        <v>4.9039999999999999</v>
-      </c>
-      <c r="F3">
-        <v>7.5999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>-473.60399999999998</v>
-      </c>
-      <c r="D4">
-        <v>960.11199999999997</v>
-      </c>
-      <c r="E4">
-        <v>7.0309999999999997</v>
-      </c>
-      <c r="F4">
-        <v>2.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>-466.88</v>
-      </c>
-      <c r="D5">
-        <v>961.346</v>
-      </c>
-      <c r="E5">
-        <v>8.2650000000000006</v>
-      </c>
-      <c r="F5">
-        <v>1.4E-2</v>
+      <c r="I26">
+        <v>963.2520087882961</v>
+      </c>
+      <c r="J26">
+        <v>10.17095097553693</v>
+      </c>
+      <c r="K26">
+        <v>8.170950975536925</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + mean_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mean_relief</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>961.3839008416803</v>
+      </c>
+      <c r="D27">
+        <v>-474.2403375176144</v>
+      </c>
+      <c r="G27">
+        <v>94</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>963.3839008416803</v>
+      </c>
+      <c r="J27">
+        <v>8.302843028921188</v>
+      </c>
+      <c r="K27">
+        <v>8.302843028921188</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + mean_relief + ecklonia + (1 | </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>957.8584619234576</v>
+      </c>
+      <c r="D28">
+        <v>-470.13802217052</v>
+      </c>
+      <c r="G28">
+        <v>92</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28">
+        <v>963.8584619234576</v>
+      </c>
+      <c r="J28">
+        <v>4.777404110698512</v>
+      </c>
+      <c r="K28">
+        <v>8.777404110698512</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>957.8584619234576</v>
+      </c>
+      <c r="D29">
+        <v>-470.13802217052</v>
+      </c>
+      <c r="G29">
+        <v>92</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29">
+        <v>963.8584619234576</v>
+      </c>
+      <c r="J29">
+        <v>4.777404110698512</v>
+      </c>
+      <c r="K29">
+        <v>8.777404110698512</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + mean_relief + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mean_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>959.8859222994413</v>
+      </c>
+      <c r="D30">
+        <v>-472.3342654975467</v>
+      </c>
+      <c r="G30">
+        <v>93</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>963.8859222994413</v>
+      </c>
+      <c r="J30">
+        <v>6.804864486682163</v>
+      </c>
+      <c r="K30">
+        <v>8.804864486682163</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + mean_relief + sd_relief + ecklonia + </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>958.087599521068</v>
+      </c>
+      <c r="D31">
+        <v>-470.2525909693252</v>
+      </c>
+      <c r="G31">
+        <v>92</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31">
+        <v>964.087599521068</v>
+      </c>
+      <c r="J31">
+        <v>5.006541708308873</v>
+      </c>
+      <c r="K31">
+        <v>9.006541708308873</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>958.087599521068</v>
+      </c>
+      <c r="D32">
+        <v>-470.2525909693252</v>
+      </c>
+      <c r="G32">
+        <v>92</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <v>964.087599521068</v>
+      </c>
+      <c r="J32">
+        <v>5.006541708308873</v>
+      </c>
+      <c r="K32">
+        <v>9.006541708308873</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + macroalgae + ecklonia + (1 | </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>depth + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>958.2077021707856</v>
+      </c>
+      <c r="D33">
+        <v>-470.312642294184</v>
+      </c>
+      <c r="G33">
+        <v>92</v>
+      </c>
+      <c r="H33">
+        <v>3</v>
+      </c>
+      <c r="I33">
+        <v>964.2077021707856</v>
+      </c>
+      <c r="J33">
+        <v>5.12664435802651</v>
+      </c>
+      <c r="K33">
+        <v>9.12664435802651</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>depth + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>958.2077021707856</v>
+      </c>
+      <c r="D34">
+        <v>-470.312642294184</v>
+      </c>
+      <c r="G34">
+        <v>92</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>964.2077021707856</v>
+      </c>
+      <c r="J34">
+        <v>5.12664435802651</v>
+      </c>
+      <c r="K34">
+        <v>9.12664435802651</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + sd_relief + ecklonia + (1 | </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>958.6051298823352</v>
+      </c>
+      <c r="D35">
+        <v>-470.5113561499588</v>
+      </c>
+      <c r="G35">
+        <v>92</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+      <c r="I35">
+        <v>964.6051298823352</v>
+      </c>
+      <c r="J35">
+        <v>5.52407206957605</v>
+      </c>
+      <c r="K35">
+        <v>9.52407206957605</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>958.6051298823352</v>
+      </c>
+      <c r="D36">
+        <v>-470.5113561499588</v>
+      </c>
+      <c r="G36">
+        <v>92</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="I36">
+        <v>964.6051298823352</v>
+      </c>
+      <c r="J36">
+        <v>5.52407206957605</v>
+      </c>
+      <c r="K36">
+        <v>9.52407206957605</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + sd_relief + macroalgae + ecklonia + </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sd_relief + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>958.7014887133474</v>
+      </c>
+      <c r="D37">
+        <v>-470.5595355654649</v>
+      </c>
+      <c r="G37">
+        <v>92</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>964.7014887133474</v>
+      </c>
+      <c r="J37">
+        <v>5.620430900588303</v>
+      </c>
+      <c r="K37">
+        <v>9.620430900588303</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sd_relief + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>958.7014887133474</v>
+      </c>
+      <c r="D38">
+        <v>-470.5595355654649</v>
+      </c>
+      <c r="G38">
+        <v>92</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+      <c r="I38">
+        <v>964.7014887133474</v>
+      </c>
+      <c r="J38">
+        <v>5.620430900588303</v>
+      </c>
+      <c r="K38">
+        <v>9.620430900588303</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + mean_relief + macroalgae + ecklonia + </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mean_relief + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>958.7671793771236</v>
+      </c>
+      <c r="D39">
+        <v>-470.592380897353</v>
+      </c>
+      <c r="G39">
+        <v>92</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>964.7671793771236</v>
+      </c>
+      <c r="J39">
+        <v>5.686121564364498</v>
+      </c>
+      <c r="K39">
+        <v>9.686121564364498</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>mean_relief + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>958.7671793771236</v>
+      </c>
+      <c r="D40">
+        <v>-470.592380897353</v>
+      </c>
+      <c r="G40">
+        <v>92</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+      <c r="I40">
+        <v>964.7671793771236</v>
+      </c>
+      <c r="J40">
+        <v>5.686121564364498</v>
+      </c>
+      <c r="K40">
+        <v>9.686121564364498</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + depth + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>depth + macroalgae</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>961.3246222438111</v>
+      </c>
+      <c r="D41">
+        <v>-473.0536154697316</v>
+      </c>
+      <c r="G41">
+        <v>93</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="I41">
+        <v>965.3246222438111</v>
+      </c>
+      <c r="J41">
+        <v>8.243564431051936</v>
+      </c>
+      <c r="K41">
+        <v>10.24356443105194</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + sd_relief + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>961.6301087112583</v>
+      </c>
+      <c r="D42">
+        <v>-473.2063587034552</v>
+      </c>
+      <c r="G42">
+        <v>93</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>965.6301087112583</v>
+      </c>
+      <c r="J42">
+        <v>8.549050898499218</v>
+      </c>
+      <c r="K42">
+        <v>10.54905089849922</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>scytothalia</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>963.8498660691633</v>
+      </c>
+      <c r="D43">
+        <v>-475.4733201313559</v>
+      </c>
+      <c r="G43">
+        <v>94</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>965.8498660691633</v>
+      </c>
+      <c r="J43">
+        <v>10.76880825640421</v>
+      </c>
+      <c r="K43">
+        <v>10.76880825640421</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + scytothalia + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>962.4195284674903</v>
+      </c>
+      <c r="D44">
+        <v>-473.6010685815712</v>
+      </c>
+      <c r="G44">
+        <v>93</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44">
+        <v>966.4195284674903</v>
+      </c>
+      <c r="J44">
+        <v>9.338470654731168</v>
+      </c>
+      <c r="K44">
+        <v>11.33847065473117</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + mean_relief + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>962.5054595794749</v>
+      </c>
+      <c r="D45">
+        <v>-473.6440341375635</v>
+      </c>
+      <c r="G45">
+        <v>93</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="I45">
+        <v>966.5054595794749</v>
+      </c>
+      <c r="J45">
+        <v>9.424401766715732</v>
+      </c>
+      <c r="K45">
+        <v>11.42440176671573</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + mean_relief + macroalgae + (1 | </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>960.8074483837052</v>
+      </c>
+      <c r="D46">
+        <v>-471.6125154006438</v>
+      </c>
+      <c r="G46">
+        <v>92</v>
+      </c>
+      <c r="H46">
+        <v>3</v>
+      </c>
+      <c r="I46">
+        <v>966.8074483837052</v>
+      </c>
+      <c r="J46">
+        <v>7.726390570946023</v>
+      </c>
+      <c r="K46">
+        <v>11.72639057094602</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>960.8074483837052</v>
+      </c>
+      <c r="D47">
+        <v>-471.6125154006438</v>
+      </c>
+      <c r="G47">
+        <v>92</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>966.8074483837052</v>
+      </c>
+      <c r="J47">
+        <v>7.726390570946023</v>
+      </c>
+      <c r="K47">
+        <v>11.72639057094602</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + mean_relief + sd_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>962.8290993816694</v>
+      </c>
+      <c r="D48">
+        <v>-473.8058540386608</v>
+      </c>
+      <c r="G48">
+        <v>93</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48">
+        <v>966.8290993816694</v>
+      </c>
+      <c r="J48">
+        <v>9.748041568910253</v>
+      </c>
+      <c r="K48">
+        <v>11.74804156891025</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + mean_relief + sd_relief + macroalgae + </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>960.9961234453192</v>
+      </c>
+      <c r="D49">
+        <v>-471.7068529314508</v>
+      </c>
+      <c r="G49">
+        <v>92</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+      <c r="I49">
+        <v>966.9961234453192</v>
+      </c>
+      <c r="J49">
+        <v>7.915065632560072</v>
+      </c>
+      <c r="K49">
+        <v>11.91506563256007</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>960.9961234453192</v>
+      </c>
+      <c r="D50">
+        <v>-471.7068529314508</v>
+      </c>
+      <c r="G50">
+        <v>92</v>
+      </c>
+      <c r="H50">
+        <v>3</v>
+      </c>
+      <c r="I50">
+        <v>966.9961234453192</v>
+      </c>
+      <c r="J50">
+        <v>7.915065632560072</v>
+      </c>
+      <c r="K50">
+        <v>11.91506563256007</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + depth + mean_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>depth + mean_relief</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>963.076875280913</v>
+      </c>
+      <c r="D51">
+        <v>-473.9297419882826</v>
+      </c>
+      <c r="G51">
+        <v>93</v>
+      </c>
+      <c r="H51">
+        <v>2</v>
+      </c>
+      <c r="I51">
+        <v>967.076875280913</v>
+      </c>
+      <c r="J51">
+        <v>9.995817468153859</v>
+      </c>
+      <c r="K51">
+        <v>11.99581746815386</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + sd_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sd_relief</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>965.192275579361</v>
+      </c>
+      <c r="D52">
+        <v>-476.1445248864547</v>
+      </c>
+      <c r="G52">
+        <v>94</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>967.192275579361</v>
+      </c>
+      <c r="J52">
+        <v>12.11121776660184</v>
+      </c>
+      <c r="K52">
+        <v>12.11121776660184</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + depth + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>965.2430813445404</v>
+      </c>
+      <c r="D53">
+        <v>-476.1699277690444</v>
+      </c>
+      <c r="G53">
+        <v>94</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>967.2430813445404</v>
+      </c>
+      <c r="J53">
+        <v>12.1620235317813</v>
+      </c>
+      <c r="K53">
+        <v>12.1620235317813</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + mean_relief + scytothalia + macroalgae + </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>962.2413205438877</v>
+      </c>
+      <c r="D54">
+        <v>-472.329451480735</v>
+      </c>
+      <c r="G54">
+        <v>92</v>
+      </c>
+      <c r="H54">
+        <v>3</v>
+      </c>
+      <c r="I54">
+        <v>968.2413205438877</v>
+      </c>
+      <c r="J54">
+        <v>9.160262731128569</v>
+      </c>
+      <c r="K54">
+        <v>13.16026273112857</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>962.2413205438877</v>
+      </c>
+      <c r="D55">
+        <v>-472.329451480735</v>
+      </c>
+      <c r="G55">
+        <v>92</v>
+      </c>
+      <c r="H55">
+        <v>3</v>
+      </c>
+      <c r="I55">
+        <v>968.2413205438877</v>
+      </c>
+      <c r="J55">
+        <v>9.160262731128569</v>
+      </c>
+      <c r="K55">
+        <v>13.16026273112857</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + sd_relief + macroalgae + (1 | </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>963.2616571474064</v>
+      </c>
+      <c r="D56">
+        <v>-472.8396197824944</v>
+      </c>
+      <c r="G56">
+        <v>92</v>
+      </c>
+      <c r="H56">
+        <v>3</v>
+      </c>
+      <c r="I56">
+        <v>969.2616571474064</v>
+      </c>
+      <c r="J56">
+        <v>10.18059933464724</v>
+      </c>
+      <c r="K56">
+        <v>14.18059933464724</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>963.2616571474064</v>
+      </c>
+      <c r="D57">
+        <v>-472.8396197824944</v>
+      </c>
+      <c r="G57">
+        <v>92</v>
+      </c>
+      <c r="H57">
+        <v>3</v>
+      </c>
+      <c r="I57">
+        <v>969.2616571474064</v>
+      </c>
+      <c r="J57">
+        <v>10.18059933464724</v>
+      </c>
+      <c r="K57">
+        <v>14.18059933464724</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + scytothalia + macroalgae + (1 | </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>depth + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>963.6866881468547</v>
+      </c>
+      <c r="D58">
+        <v>-473.0521352822186</v>
+      </c>
+      <c r="G58">
+        <v>92</v>
+      </c>
+      <c r="H58">
+        <v>3</v>
+      </c>
+      <c r="I58">
+        <v>969.6866881468547</v>
+      </c>
+      <c r="J58">
+        <v>10.60563033409562</v>
+      </c>
+      <c r="K58">
+        <v>14.60563033409562</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>depth + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>963.6866881468547</v>
+      </c>
+      <c r="D59">
+        <v>-473.0521352822186</v>
+      </c>
+      <c r="G59">
+        <v>92</v>
+      </c>
+      <c r="H59">
+        <v>3</v>
+      </c>
+      <c r="I59">
+        <v>969.6866881468547</v>
+      </c>
+      <c r="J59">
+        <v>10.60563033409562</v>
+      </c>
+      <c r="K59">
+        <v>14.60563033409562</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + depth + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>depth + scytothalia</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>965.8786685565117</v>
+      </c>
+      <c r="D60">
+        <v>-475.3306386260819</v>
+      </c>
+      <c r="G60">
+        <v>93</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="I60">
+        <v>969.8786685565117</v>
+      </c>
+      <c r="J60">
+        <v>12.79761074375256</v>
+      </c>
+      <c r="K60">
+        <v>14.79761074375256</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + sd_relief + scytothalia + macroalgae + </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>963.9480943167166</v>
+      </c>
+      <c r="D61">
+        <v>-473.1828383671495</v>
+      </c>
+      <c r="G61">
+        <v>92</v>
+      </c>
+      <c r="H61">
+        <v>3</v>
+      </c>
+      <c r="I61">
+        <v>969.9480943167166</v>
+      </c>
+      <c r="J61">
+        <v>10.86703650395748</v>
+      </c>
+      <c r="K61">
+        <v>14.86703650395748</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>963.9480943167166</v>
+      </c>
+      <c r="D62">
+        <v>-473.1828383671495</v>
+      </c>
+      <c r="G62">
+        <v>92</v>
+      </c>
+      <c r="H62">
+        <v>3</v>
+      </c>
+      <c r="I62">
+        <v>969.9480943167166</v>
+      </c>
+      <c r="J62">
+        <v>10.86703650395748</v>
+      </c>
+      <c r="K62">
+        <v>14.86703650395748</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + sd_relief + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>966.0530807483842</v>
+      </c>
+      <c r="D63">
+        <v>-475.4178447220182</v>
+      </c>
+      <c r="G63">
+        <v>93</v>
+      </c>
+      <c r="H63">
+        <v>2</v>
+      </c>
+      <c r="I63">
+        <v>970.0530807483842</v>
+      </c>
+      <c r="J63">
+        <v>12.97202293562509</v>
+      </c>
+      <c r="K63">
+        <v>14.97202293562509</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + mean_relief + scytothalia + </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>964.2664223419702</v>
+      </c>
+      <c r="D64">
+        <v>-473.3420023797763</v>
+      </c>
+      <c r="G64">
+        <v>92</v>
+      </c>
+      <c r="H64">
+        <v>3</v>
+      </c>
+      <c r="I64">
+        <v>970.2664223419702</v>
+      </c>
+      <c r="J64">
+        <v>11.18536452921103</v>
+      </c>
+      <c r="K64">
+        <v>15.18536452921103</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>964.2664223419702</v>
+      </c>
+      <c r="D65">
+        <v>-473.3420023797763</v>
+      </c>
+      <c r="G65">
+        <v>92</v>
+      </c>
+      <c r="H65">
+        <v>3</v>
+      </c>
+      <c r="I65">
+        <v>970.2664223419702</v>
+      </c>
+      <c r="J65">
+        <v>11.18536452921103</v>
+      </c>
+      <c r="K65">
+        <v>15.18536452921103</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + mean_relief + sd_relief + scytothalia + </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>964.3409514125044</v>
+      </c>
+      <c r="D66">
+        <v>-473.3792669150434</v>
+      </c>
+      <c r="G66">
+        <v>92</v>
+      </c>
+      <c r="H66">
+        <v>3</v>
+      </c>
+      <c r="I66">
+        <v>970.3409514125044</v>
+      </c>
+      <c r="J66">
+        <v>11.25989359974528</v>
+      </c>
+      <c r="K66">
+        <v>15.25989359974528</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (1 | location)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>964.3409514125044</v>
+      </c>
+      <c r="D67">
+        <v>-473.3792669150434</v>
+      </c>
+      <c r="G67">
+        <v>92</v>
+      </c>
+      <c r="H67">
+        <v>3</v>
+      </c>
+      <c r="I67">
+        <v>970.3409514125044</v>
+      </c>
+      <c r="J67">
+        <v>11.25989359974528</v>
+      </c>
+      <c r="K67">
+        <v>15.25989359974528</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + mean_relief + sd_relief + (1 | </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + sd_relief</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>964.8379003756932</v>
+      </c>
+      <c r="D68">
+        <v>-473.6277413966378</v>
+      </c>
+      <c r="G68">
+        <v>92</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>970.8379003756932</v>
+      </c>
+      <c r="J68">
+        <v>11.75684256293403</v>
+      </c>
+      <c r="K68">
+        <v>15.75684256293403</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + sd_relief</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>964.8379003756932</v>
+      </c>
+      <c r="D69">
+        <v>-473.6277413966378</v>
+      </c>
+      <c r="G69">
+        <v>92</v>
+      </c>
+      <c r="H69">
+        <v>3</v>
+      </c>
+      <c r="I69">
+        <v>970.8379003756932</v>
+      </c>
+      <c r="J69">
+        <v>11.75684256293403</v>
+      </c>
+      <c r="K69">
+        <v>15.75684256293403</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>total_abundance ~ bait + depth + sd_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>depth + sd_relief</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>967.3597576533612</v>
+      </c>
+      <c r="D70">
+        <v>-476.0711831745066</v>
+      </c>
+      <c r="G70">
+        <v>93</v>
+      </c>
+      <c r="H70">
+        <v>2</v>
+      </c>
+      <c r="I70">
+        <v>971.3597576533612</v>
+      </c>
+      <c r="J70">
+        <v>14.27869984060203</v>
+      </c>
+      <c r="K70">
+        <v>16.27869984060203</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_abundance ~ bait + depth + sd_relief + scytothalia + (1 | </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>968.2054648070847</v>
+      </c>
+      <c r="D71">
+        <v>-475.3115236123335</v>
+      </c>
+      <c r="G71">
+        <v>92</v>
+      </c>
+      <c r="H71">
+        <v>3</v>
+      </c>
+      <c r="I71">
+        <v>974.2054648070847</v>
+      </c>
+      <c r="J71">
+        <v>15.12440699432557</v>
+      </c>
+      <c r="K71">
+        <v>19.12440699432557</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>968.2054648070847</v>
+      </c>
+      <c r="D72">
+        <v>-475.3115236123335</v>
+      </c>
+      <c r="G72">
+        <v>92</v>
+      </c>
+      <c r="H72">
+        <v>3</v>
+      </c>
+      <c r="I72">
+        <v>974.2054648070847</v>
+      </c>
+      <c r="J72">
+        <v>15.12440699432557</v>
+      </c>
+      <c r="K72">
+        <v>19.12440699432557</v>
       </c>
     </row>
   </sheetData>
